--- a/jogos_2024-11-06.xlsx
+++ b/jogos_2024-11-06.xlsx
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,28 +1443,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
       <c r="N8" t="n">
-        <v>3.48</v>
+        <v>1.93</v>
       </c>
       <c r="O8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.63</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.75</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>2.63</v>
@@ -1473,53 +1473,53 @@
         <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="X8" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['31', '41']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="AI8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45602.61458333334</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,28 +1572,28 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3.75</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.63</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
         <v>2.63</v>
@@ -1602,53 +1602,53 @@
         <v>1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="X9" t="n">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['31', '41']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI9" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['52']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45602.61458333334</v>
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.25</v>
+        <v>2.02</v>
       </c>
       <c r="M11" t="n">
-        <v>3.41</v>
+        <v>3.49</v>
       </c>
       <c r="N11" t="n">
-        <v>1.87</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="P11" t="n">
         <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA11" t="n">
         <v>3.25</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W11" t="n">
+      <c r="AB11" t="n">
         <v>1.35</v>
       </c>
-      <c r="X11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AC11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD11" t="n">
         <v>2</v>
       </c>
-      <c r="Z11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['57', '85']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.8</v>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI11" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45602.69791666666</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.83</v>
+        <v>4.25</v>
       </c>
       <c r="M12" t="n">
-        <v>3.61</v>
+        <v>3.41</v>
       </c>
       <c r="N12" t="n">
-        <v>4.13</v>
+        <v>1.87</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
         <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.91</v>
       </c>
-      <c r="AA12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['11', '73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.53</v>
+        <v>2.63</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45602.69791666666</v>
@@ -2062,16 +2062,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>3.49</v>
+        <v>3.61</v>
       </c>
       <c r="N13" t="n">
-        <v>3.55</v>
+        <v>4.13</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
@@ -2118,53 +2118,53 @@
         <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
         <v>1.3</v>
       </c>
       <c r="X13" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['57', '85']</t>
+          <t>['11', '73']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45602.69791666666</v>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,80 +2217,80 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.12</v>
+        <v>2.68</v>
       </c>
       <c r="M14" t="n">
-        <v>3.76</v>
+        <v>3.19</v>
       </c>
       <c r="N14" t="n">
-        <v>3.08</v>
+        <v>2.68</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T14" t="n">
         <v>3.25</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.1</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="X14" t="n">
-        <v>6.2</v>
+        <v>3.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
+          <t>['45+3']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['51', '88']</t>
-        </is>
-      </c>
       <c r="AG14" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AJ14" t="n">
         <v>2.1</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,22 +2346,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>3.22</v>
       </c>
       <c r="M15" t="n">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>2.27</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
@@ -2370,59 +2370,59 @@
         <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="X15" t="n">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z15" t="n">
         <v>1.75</v>
       </c>
-      <c r="Z15" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AA15" t="n">
-        <v>3.35</v>
+        <v>4.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['37', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45602.70833333334</v>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="M16" t="n">
-        <v>3.19</v>
+        <v>3.48</v>
       </c>
       <c r="N16" t="n">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD16" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['37', '79']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['45+3']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45602.70833333334</v>
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="M17" t="n">
-        <v>4.55</v>
+        <v>3.76</v>
       </c>
       <c r="N17" t="n">
-        <v>5.45</v>
+        <v>3.08</v>
       </c>
       <c r="O17" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
         <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V17" t="n">
         <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['45+2', '58', '86']</t>
+          <t>['51', '88']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.52</v>
+        <v>1.69</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45602.70833333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.22</v>
+        <v>1.86</v>
       </c>
       <c r="M18" t="n">
-        <v>3.24</v>
+        <v>3.53</v>
       </c>
       <c r="N18" t="n">
-        <v>2.27</v>
+        <v>4.12</v>
       </c>
       <c r="O18" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['18', '90+3']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>2.88</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45602.70833333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.66</v>
+        <v>4.55</v>
       </c>
       <c r="N19" t="n">
-        <v>4.04</v>
+        <v>5.45</v>
       </c>
       <c r="O19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P19" t="n">
         <v>2.5</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
+        <v>5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD19" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2', '58', '86']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.9</v>
+        <v>2.52</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45602.70833333334</v>
@@ -2955,35 +2955,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.35</v>
+        <v>10.85</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8</v>
+        <v>7.24</v>
       </c>
       <c r="N20" t="n">
-        <v>3.5</v>
+        <v>1.19</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="P20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T20" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.1</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.49</v>
-      </c>
       <c r="X20" t="n">
-        <v>2.54</v>
+        <v>7.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.88</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.16</v>
+        <v>1.93</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['27', '84']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['13', '43', '53', '55', '76']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.63</v>
+        <v>1.02</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.83</v>
+        <v>4.75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.6</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45602.70833333334</v>
@@ -3084,32 +3084,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>3.53</v>
+        <v>2.8</v>
       </c>
       <c r="N21" t="n">
-        <v>4.12</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S21" t="n">
         <v>2.38</v>
       </c>
-      <c r="P21" t="n">
+      <c r="T21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z21" t="n">
+      <c r="AD21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.83</v>
       </c>
-      <c r="AA21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['14']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['18', '90+3']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45602.70833333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>10.85</v>
+        <v>1.84</v>
       </c>
       <c r="M22" t="n">
-        <v>7.24</v>
+        <v>3.66</v>
       </c>
       <c r="N22" t="n">
-        <v>1.19</v>
+        <v>4.04</v>
       </c>
       <c r="O22" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.53</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
         <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="X22" t="n">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.9</v>
+        <v>1.93</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>3.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>1.38</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['27', '84']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['13', '43', '53', '55', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>5</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.75</v>
+        <v>1.53</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.17</v>
+        <v>2.75</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45602.70833333334</v>
